--- a/artfynd/A 10182-2026 artfynd.xlsx
+++ b/artfynd/A 10182-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,6 +877,125 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131468214</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57076</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fästampen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>369868</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6414694</v>
+      </c>
+      <c r="S4" t="n">
+        <v>16</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bredared</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Nyberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Nyberg, Per Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10182-2026 artfynd.xlsx
+++ b/artfynd/A 10182-2026 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>131468214</v>
       </c>
       <c r="B4" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10182-2026 artfynd.xlsx
+++ b/artfynd/A 10182-2026 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>131468214</v>
       </c>
       <c r="B4" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10182-2026 artfynd.xlsx
+++ b/artfynd/A 10182-2026 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>131468214</v>
       </c>
       <c r="B4" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10182-2026 artfynd.xlsx
+++ b/artfynd/A 10182-2026 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>131468214</v>
       </c>
       <c r="B4" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10182-2026 artfynd.xlsx
+++ b/artfynd/A 10182-2026 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>131468214</v>
       </c>
       <c r="B4" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10182-2026 artfynd.xlsx
+++ b/artfynd/A 10182-2026 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>131468214</v>
       </c>
       <c r="B4" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10182-2026 artfynd.xlsx
+++ b/artfynd/A 10182-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125164879</v>
+        <v>131467778</v>
       </c>
       <c r="B2" t="n">
-        <v>97212</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>369872</v>
+        <v>369677</v>
       </c>
       <c r="R2" t="n">
-        <v>6414698</v>
+        <v>6414533</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,12 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -758,29 +780,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Per Nyberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Per Nyberg, Per Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125164903</v>
+        <v>131468214</v>
       </c>
       <c r="B3" t="n">
-        <v>97209</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,27 +809,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -816,13 +845,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>369782</v>
+        <v>369868</v>
       </c>
       <c r="R3" t="n">
-        <v>6414762</v>
+        <v>6414694</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -846,12 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -860,29 +899,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Per Nyberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tim Hipkiss</t>
+          <t>Per Nyberg, Per Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131468214</v>
+        <v>125164903</v>
       </c>
       <c r="B4" t="n">
-        <v>57102</v>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,35 +928,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -926,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>369868</v>
+        <v>369782</v>
       </c>
       <c r="R4" t="n">
-        <v>6414694</v>
+        <v>6414762</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,22 +986,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:21</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:21</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,21 +1000,124 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Nyberg</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Nyberg, Per Johansson</t>
+          <t>Tim Hipkiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125164879</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fästampen, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>369872</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6414698</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bredared</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10182-2026 artfynd.xlsx
+++ b/artfynd/A 10182-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131467778</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131468214</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125164903</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,8 +1138,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125164879</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>